--- a/UnityTableTool/Data/ValidationExamples/09_VALID_ENUM_ARRAY.xlsx
+++ b/UnityTableTool/Data/ValidationExamples/09_VALID_ENUM_ARRAY.xlsx
@@ -1,96 +1,1002 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALID_ENUM_ARRAY" sheetId="1" r:id="Ra005744e6bb34878"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\ValidationExamples\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowWidth="25320" windowHeight="17175" activeTab="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="VALID_ENUM_ARRAY" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t>table: VALID_ENUM_ARRAY</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>enum(enum1|enum2)()</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>cs</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>enum1#enum2#enum1</t>
+  </si>
+  <si>
+    <t>table: TABLE_NOT_FORMAL</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF1F2937"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FF163A5F"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF374151"/>
-      <x:name val="Arial"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="4">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE8F0F7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF5F7FA"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="8">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="0"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF163A5F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF374151"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2937"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="35">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F0F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -281,50 +1187,84 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>table: VALID_ENUM_ARRAY</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>说明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="7" t="str">
-        <x:v>enum(enum1|enum2)()</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="7" t="str">
-        <x:v>id</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="7" t="str">
-        <x:v>cs</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="7" t="str"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="3" t="str">
-        <x:v>enum1#enum2#enum1</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" outlineLevelRow="3"/>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:1">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:1">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" spans="1:1">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>